--- a/artfynd/A 58906-2021 artfynd.xlsx
+++ b/artfynd/A 58906-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58906-2021 artfynd.xlsx
+++ b/artfynd/A 58906-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,137 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123435110</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56691</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Krakmossen, Krakmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630859</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6647439</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58906-2021 artfynd.xlsx
+++ b/artfynd/A 58906-2021 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>123435110</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58906-2021 artfynd.xlsx
+++ b/artfynd/A 58906-2021 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>123435110</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58906-2021 artfynd.xlsx
+++ b/artfynd/A 58906-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>73618980</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630560.979099418</v>
+        <v>630561</v>
       </c>
       <c r="R2" t="n">
-        <v>6646973.019647193</v>
+        <v>6646973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123435110</v>
+        <v>75099144</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,37 +812,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krakmossen, Krakmossen, Upl</t>
+          <t>Fäbodmossen, intill NR, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630859</v>
+        <v>630488</v>
       </c>
       <c r="R3" t="n">
-        <v>6647439</v>
+        <v>6646986</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2012-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2012-04-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 hönor på en skogsbilväg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +881,255 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123435110</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Krakmossen, Krakmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630859</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6647439</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Emil V. Nilsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Emil V. Nilsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103371326</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fäbodmossen öster om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630654</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6647081</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
